--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化_性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化_性別.xlsx
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>603.14869999999996</v>
+        <v>606.4973</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>19.998182112662747</v>
+        <v>20.048176298852031</v>
       </c>
       <c r="F2" s="0">
-        <v>-3.0018178873372534</v>
+        <v>-2.9518237011479691</v>
       </c>
       <c r="G2" s="0">
-        <v>3.0018178873372534</v>
+        <v>2.9518237011479691</v>
       </c>
       <c r="H2" s="0">
-        <v>19.498182112662747</v>
+        <v>19.548176298852031</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.5018178873372534</v>
+        <v>-3.4518237011479691</v>
       </c>
       <c r="J2" s="0">
-        <v>3.5018178873372534</v>
+        <v>3.4518237011479691</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>609.20730000000003</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.006535964564368</v>
+        <v>19.974728939315419</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.99346403543563255</v>
+        <v>-1.025271060684581</v>
       </c>
       <c r="G3" s="0">
-        <v>0.99346403543563255</v>
+        <v>1.025271060684581</v>
       </c>
       <c r="H3" s="0">
-        <v>19.506535964564368</v>
+        <v>19.474728939315419</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.4934640354356326</v>
+        <v>-1.525271060684581</v>
       </c>
       <c r="J3" s="0">
-        <v>1.4934640354356326</v>
+        <v>1.525271060684581</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>755.06500000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>23.181845368995504</v>
+        <v>22.859785352621877</v>
       </c>
       <c r="F4" s="0">
-        <v>-0.31815463100449648</v>
+        <v>-0.64021464737812295</v>
       </c>
       <c r="G4" s="0">
-        <v>0.31815463100449648</v>
+        <v>0.64021464737812295</v>
       </c>
       <c r="H4" s="0">
-        <v>22.681845368995504</v>
+        <v>22.359785352621877</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.81815463100449648</v>
+        <v>-1.1402146473781229</v>
       </c>
       <c r="J4" s="0">
-        <v>0.81815463100449648</v>
+        <v>1.1402146473781229</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>579.86080000000004</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.621377904524888</v>
+        <v>19.593311171530807</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.3786220954751123</v>
+        <v>-1.4066888284691928</v>
       </c>
       <c r="G5" s="0">
-        <v>1.3786220954751123</v>
+        <v>1.4066888284691928</v>
       </c>
       <c r="H5" s="0">
-        <v>19.121377904524888</v>
+        <v>19.093311171530807</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.8786220954751123</v>
+        <v>-1.9066888284691927</v>
       </c>
       <c r="J5" s="0">
-        <v>1.8786220954751123</v>
+        <v>1.9066888284691927</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>634.26990000000001</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>20.455223175378333</v>
+        <v>20.388254158856995</v>
       </c>
       <c r="F6" s="0">
-        <v>-1.0447768246216675</v>
+        <v>-1.111745841143005</v>
       </c>
       <c r="G6" s="0">
-        <v>1.0447768246216675</v>
+        <v>1.111745841143005</v>
       </c>
       <c r="H6" s="0">
-        <v>19.955223175378333</v>
+        <v>19.888254158856995</v>
       </c>
       <c r="I6" s="0">
-        <v>-1.5447768246216675</v>
+        <v>-1.611745841143005</v>
       </c>
       <c r="J6" s="0">
-        <v>1.5447768246216675</v>
+        <v>1.611745841143005</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>691.86599999999999</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>22.372006573194561</v>
+        <v>21.491383651673878</v>
       </c>
       <c r="F7" s="0">
-        <v>0.37200657319456099</v>
+        <v>-0.50861634832612168</v>
       </c>
       <c r="G7" s="0">
-        <v>0.37200657319456099</v>
+        <v>0.50861634832612168</v>
       </c>
       <c r="H7" s="0">
-        <v>21.872006573194561</v>
+        <v>20.991383651673878</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.12799342680543901</v>
+        <v>-1.0086163483261217</v>
       </c>
       <c r="J7" s="0">
-        <v>0.12799342680543901</v>
+        <v>1.0086163483261217</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>763.82230000000004</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.439566137692832</v>
+        <v>23.615800372754976</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.5604338623071676</v>
+        <v>-1.3841996272450245</v>
       </c>
       <c r="G8" s="0">
-        <v>1.5604338623071676</v>
+        <v>1.3841996272450245</v>
       </c>
       <c r="H8" s="0">
-        <v>22.939566137692832</v>
+        <v>23.115800372754976</v>
       </c>
       <c r="I8" s="0">
-        <v>-2.0604338623071676</v>
+        <v>-1.8841996272450246</v>
       </c>
       <c r="J8" s="0">
-        <v>2.0604338623071676</v>
+        <v>1.8841996272450246</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>607.71310000000005</v>
+        <v>612.55169999999998</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.510682395799901</v>
+        <v>20.55294803455314</v>
       </c>
       <c r="F9" s="0">
-        <v>0.01068239579990049</v>
+        <v>0.052948034553139678</v>
       </c>
       <c r="G9" s="0">
-        <v>0.01068239579990049</v>
+        <v>0.052948034553139678</v>
       </c>
       <c r="H9" s="0">
-        <v>20.010682395799901</v>
+        <v>20.05294803455314</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.48931760420009951</v>
+        <v>-0.44705196544686032</v>
       </c>
       <c r="J9" s="0">
-        <v>0.48931760420009951</v>
+        <v>0.44705196544686032</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>641.99860000000001</v>
+        <v>647.83249999999998</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.234507227422654</v>
+        <v>21.337387636050501</v>
       </c>
       <c r="F10" s="0">
-        <v>0.23450722742265384</v>
+        <v>0.33738763605050082</v>
       </c>
       <c r="G10" s="0">
-        <v>0.23450722742265384</v>
+        <v>0.33738763605050082</v>
       </c>
       <c r="H10" s="0">
-        <v>20.734507227422654</v>
+        <v>20.837387636050501</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.26549277257734616</v>
+        <v>-0.16261236394949918</v>
       </c>
       <c r="J10" s="0">
-        <v>0.26549277257734616</v>
+        <v>0.16261236394949918</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>463.59699999999998</v>
+        <v>468.75369999999998</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.078870667471215</v>
+        <v>19.124147908288165</v>
       </c>
       <c r="F11" s="0">
-        <v>1.0788706674712145</v>
+        <v>1.1241479082881654</v>
       </c>
       <c r="G11" s="0">
-        <v>1.0788706674712145</v>
+        <v>1.1241479082881654</v>
       </c>
       <c r="H11" s="0">
-        <v>18.578870667471215</v>
+        <v>18.624147908288165</v>
       </c>
       <c r="I11" s="0">
-        <v>0.57887066747121452</v>
+        <v>0.62414790828816535</v>
       </c>
       <c r="J11" s="0">
-        <v>0.57887066747121452</v>
+        <v>0.62414790828816535</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>745.02800000000002</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>21.825637651418063</v>
+        <v>21.84476871927604</v>
       </c>
       <c r="F12" s="0">
-        <v>-3.174362348581937</v>
+        <v>-3.1552312807239602</v>
       </c>
       <c r="G12" s="0">
-        <v>3.174362348581937</v>
+        <v>3.1552312807239602</v>
       </c>
       <c r="H12" s="0">
-        <v>21.325637651418063</v>
+        <v>21.34476871927604</v>
       </c>
       <c r="I12" s="0">
-        <v>-3.674362348581937</v>
+        <v>-3.6552312807239602</v>
       </c>
       <c r="J12" s="0">
-        <v>3.674362348581937</v>
+        <v>3.6552312807239602</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>674.10310000000004</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.709765885463789</v>
+        <v>21.635010193967204</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.79023411453621151</v>
+        <v>-0.86498980603279563</v>
       </c>
       <c r="G13" s="0">
-        <v>0.79023411453621151</v>
+        <v>0.86498980603279563</v>
       </c>
       <c r="H13" s="0">
-        <v>21.209765885463789</v>
+        <v>21.135010193967204</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.2902341145362115</v>
+        <v>-1.3649898060327956</v>
       </c>
       <c r="J13" s="0">
-        <v>1.2902341145362115</v>
+        <v>1.3649898060327956</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>678.64329999999995</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.433374791881132</v>
+        <v>21.441165679712618</v>
       </c>
       <c r="F14" s="0">
-        <v>0.93337479188113193</v>
+        <v>0.94116567971261844</v>
       </c>
       <c r="G14" s="0">
-        <v>0.93337479188113193</v>
+        <v>0.94116567971261844</v>
       </c>
       <c r="H14" s="0">
-        <v>20.933374791881132</v>
+        <v>20.941165679712618</v>
       </c>
       <c r="I14" s="0">
-        <v>0.43337479188113193</v>
+        <v>0.44116567971261844</v>
       </c>
       <c r="J14" s="0">
-        <v>0.43337479188113193</v>
+        <v>0.44116567971261844</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>588.29200000000003</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>19.843355496928442</v>
+        <v>19.878903767386611</v>
       </c>
       <c r="F15" s="0">
-        <v>0.34335549692844225</v>
+        <v>0.37890376738661047</v>
       </c>
       <c r="G15" s="0">
-        <v>0.34335549692844225</v>
+        <v>0.37890376738661047</v>
       </c>
       <c r="H15" s="0">
-        <v>19.343355496928442</v>
+        <v>19.378903767386611</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.15664450307155775</v>
+        <v>-0.12109623261338953</v>
       </c>
       <c r="J15" s="0">
-        <v>0.15664450307155775</v>
+        <v>0.12109623261338953</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>0</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.86260000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>20.69431942064465</v>
+        <v>20.680198895703455</v>
       </c>
       <c r="F16" s="0">
-        <v>1.1943194206446499</v>
+        <v>1.1801988957034553</v>
       </c>
       <c r="G16" s="0">
-        <v>1.1943194206446499</v>
+        <v>1.1801988957034553</v>
       </c>
       <c r="H16" s="0">
-        <v>20.19431942064465</v>
+        <v>20.180198895703455</v>
       </c>
       <c r="I16" s="0">
-        <v>0.69431942064464991</v>
+        <v>0.68019889570345526</v>
       </c>
       <c r="J16" s="0">
-        <v>0.69431942064464991</v>
+        <v>0.68019889570345526</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>565.14229999999998</v>
+        <v>557.87480000000005</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.628614060735352</v>
+        <v>19.481749475778226</v>
       </c>
       <c r="F17" s="0">
-        <v>1.1286140607353517</v>
+        <v>0.98174947577822635</v>
       </c>
       <c r="G17" s="0">
-        <v>1.1286140607353517</v>
+        <v>0.98174947577822635</v>
       </c>
       <c r="H17" s="0">
-        <v>19.128614060735352</v>
+        <v>18.981749475778226</v>
       </c>
       <c r="I17" s="0">
-        <v>0.62861406073535164</v>
+        <v>0.48174947577822636</v>
       </c>
       <c r="J17" s="0">
-        <v>0.62861406073535164</v>
+        <v>0.48174947577822636</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>726.14229999999998</v>
+        <v>734.02059999999995</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>21.902624937077661</v>
+        <v>21.875463014787329</v>
       </c>
       <c r="F18" s="0">
-        <v>-1.8473750629223389</v>
+        <v>-1.8745369852126714</v>
       </c>
       <c r="G18" s="0">
-        <v>1.8473750629223389</v>
+        <v>1.8745369852126714</v>
       </c>
       <c r="H18" s="0">
-        <v>21.402624937077661</v>
+        <v>21.375463014787329</v>
       </c>
       <c r="I18" s="0">
-        <v>-2.3473750629223389</v>
+        <v>-2.3745369852126714</v>
       </c>
       <c r="J18" s="0">
-        <v>2.3473750629223389</v>
+        <v>2.3745369852126714</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>674.8356</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.889398390248065</v>
+        <v>20.98703884767173</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.3606016097519351</v>
+        <v>-1.2629611523282698</v>
       </c>
       <c r="G19" s="0">
-        <v>1.3606016097519351</v>
+        <v>1.2629611523282698</v>
       </c>
       <c r="H19" s="0">
-        <v>20.389398390248065</v>
+        <v>20.48703884767173</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.8606016097519351</v>
+        <v>-1.7629611523282698</v>
       </c>
       <c r="J19" s="0">
-        <v>1.8606016097519351</v>
+        <v>1.7629611523282698</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>758.93589999999995</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.162537176867904</v>
+        <v>23.426257101586071</v>
       </c>
       <c r="F20" s="0">
-        <v>-2.3374628231320962</v>
+        <v>-2.0737428984139292</v>
       </c>
       <c r="G20" s="0">
-        <v>2.3374628231320962</v>
+        <v>2.0737428984139292</v>
       </c>
       <c r="H20" s="0">
-        <v>22.662537176867904</v>
+        <v>22.926257101586071</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.8374628231320962</v>
+        <v>-2.5737428984139292</v>
       </c>
       <c r="J20" s="0">
-        <v>2.8374628231320962</v>
+        <v>2.5737428984139292</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>526.39779999999996</v>
+        <v>530.03160000000003</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>17.96851382834231</v>
+        <v>17.994687511701528</v>
       </c>
       <c r="F21" s="0">
-        <v>-4.53148617165769</v>
+        <v>-4.5053124882984719</v>
       </c>
       <c r="G21" s="0">
-        <v>4.53148617165769</v>
+        <v>4.5053124882984719</v>
       </c>
       <c r="H21" s="0">
-        <v>17.46851382834231</v>
+        <v>17.494687511701528</v>
       </c>
       <c r="I21" s="0">
-        <v>-5.03148617165769</v>
+        <v>-5.0053124882984719</v>
       </c>
       <c r="J21" s="0">
-        <v>5.03148617165769</v>
+        <v>5.0053124882984719</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>619.3691</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.494158787155261</v>
+        <v>20.376087491662048</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.0058412128447394</v>
+        <v>-1.123912508337952</v>
       </c>
       <c r="G22" s="0">
-        <v>1.0058412128447394</v>
+        <v>1.123912508337952</v>
       </c>
       <c r="H22" s="0">
-        <v>19.994158787155261</v>
+        <v>19.876087491662048</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.5058412128447394</v>
+        <v>-1.623912508337952</v>
       </c>
       <c r="J22" s="0">
-        <v>1.5058412128447394</v>
+        <v>1.623912508337952</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>681.04340000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.41815651350667</v>
+        <v>21.526627645175019</v>
       </c>
       <c r="F23" s="0">
-        <v>1.4181565135066698</v>
+        <v>1.5266276451750187</v>
       </c>
       <c r="G23" s="0">
-        <v>1.4181565135066698</v>
+        <v>1.5266276451750187</v>
       </c>
       <c r="H23" s="0">
-        <v>20.91815651350667</v>
+        <v>21.026627645175019</v>
       </c>
       <c r="I23" s="0">
-        <v>0.91815651350666982</v>
+        <v>1.0266276451750187</v>
       </c>
       <c r="J23" s="0">
-        <v>0.91815651350666982</v>
+        <v>1.0266276451750187</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>585.4384</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.692763410306004</v>
+        <v>19.662705903054089</v>
       </c>
       <c r="F24" s="0">
-        <v>0.19276341030600364</v>
+        <v>0.16270590305408916</v>
       </c>
       <c r="G24" s="0">
-        <v>0.19276341030600364</v>
+        <v>0.16270590305408916</v>
       </c>
       <c r="H24" s="0">
-        <v>19.192763410306004</v>
+        <v>19.162705903054089</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.30723658969399636</v>
+        <v>-0.33729409694591084</v>
       </c>
       <c r="J24" s="0">
-        <v>0.30723658969399636</v>
+        <v>0.33729409694591084</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>581.173</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.71926759889821</v>
+        <v>19.738637137464473</v>
       </c>
       <c r="F25" s="0">
-        <v>1.2192675988982096</v>
+        <v>1.2386371374644725</v>
       </c>
       <c r="G25" s="0">
-        <v>1.2192675988982096</v>
+        <v>1.2386371374644725</v>
       </c>
       <c r="H25" s="0">
-        <v>19.21926759889821</v>
+        <v>19.238637137464473</v>
       </c>
       <c r="I25" s="0">
-        <v>0.71926759889820957</v>
+        <v>0.73863713746447246</v>
       </c>
       <c r="J25" s="0">
-        <v>0.71926759889820957</v>
+        <v>0.73863713746447246</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>692.99239999999998</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>21.831059645789491</v>
+        <v>21.810252713772837</v>
       </c>
       <c r="F26" s="0">
-        <v>0.58105964578949099</v>
+        <v>0.56025271377283659</v>
       </c>
       <c r="G26" s="0">
-        <v>0.58105964578949099</v>
+        <v>0.56025271377283659</v>
       </c>
       <c r="H26" s="0">
-        <v>21.331059645789491</v>
+        <v>21.310252713772837</v>
       </c>
       <c r="I26" s="0">
-        <v>0.081059645789490986</v>
+        <v>0.060252713772836586</v>
       </c>
       <c r="J26" s="0">
-        <v>0.081059645789490986</v>
+        <v>0.060252713772836586</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>643.06439999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.860125026987838</v>
+        <v>20.813139483663658</v>
       </c>
       <c r="F27" s="0">
-        <v>1.6101250269878378</v>
+        <v>1.5631394836636581</v>
       </c>
       <c r="G27" s="0">
-        <v>1.6101250269878378</v>
+        <v>1.5631394836636581</v>
       </c>
       <c r="H27" s="0">
-        <v>20.360125026987838</v>
+        <v>20.313139483663658</v>
       </c>
       <c r="I27" s="0">
-        <v>1.1101250269878378</v>
+        <v>1.0631394836636581</v>
       </c>
       <c r="J27" s="0">
-        <v>1.1101250269878378</v>
+        <v>1.0631394836636581</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>679.27729999999997</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.488437953868708</v>
+        <v>21.187297558968847</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.26156204613129219</v>
+        <v>-0.56270244103115275</v>
       </c>
       <c r="G28" s="0">
-        <v>0.26156204613129219</v>
+        <v>0.56270244103115275</v>
       </c>
       <c r="H28" s="0">
-        <v>20.988437953868708</v>
+        <v>20.687297558968847</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.76156204613129219</v>
+        <v>-1.0627024410311528</v>
       </c>
       <c r="J28" s="0">
-        <v>0.76156204613129219</v>
+        <v>1.0627024410311528</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>527.95719999999994</v>
+        <v>531.55600000000004</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.185614291506919</v>
+        <v>19.179552814506863</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.5643857084930808</v>
+        <v>-1.570447185493137</v>
       </c>
       <c r="G29" s="0">
-        <v>1.5643857084930808</v>
+        <v>1.570447185493137</v>
       </c>
       <c r="H29" s="0">
-        <v>18.685614291506919</v>
+        <v>18.679552814506863</v>
       </c>
       <c r="I29" s="0">
-        <v>-2.0643857084930808</v>
+        <v>-2.070447185493137</v>
       </c>
       <c r="J29" s="0">
-        <v>2.0643857084930808</v>
+        <v>2.070447185493137</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>685.61059999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>22.256592484983401</v>
+        <v>22.340707442144783</v>
       </c>
       <c r="F30" s="0">
-        <v>0.75659248498340048</v>
+        <v>0.8407074421447831</v>
       </c>
       <c r="G30" s="0">
-        <v>0.75659248498340048</v>
+        <v>0.8407074421447831</v>
       </c>
       <c r="H30" s="0">
-        <v>21.756592484983401</v>
+        <v>21.840707442144783</v>
       </c>
       <c r="I30" s="0">
-        <v>0.25659248498340048</v>
+        <v>0.3407074421447831</v>
       </c>
       <c r="J30" s="0">
-        <v>0.25659248498340048</v>
+        <v>0.3407074421447831</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>1</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>678.49210000000005</v>
+        <v>683.32539999999995</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>22.128927901536628</v>
+        <v>22.27681059416938</v>
       </c>
       <c r="F31" s="0">
-        <v>2.6289279015366276</v>
+        <v>2.7768105941693797</v>
       </c>
       <c r="G31" s="0">
-        <v>2.6289279015366276</v>
+        <v>2.7768105941693797</v>
       </c>
       <c r="H31" s="0">
-        <v>21.628927901536628</v>
+        <v>21.77681059416938</v>
       </c>
       <c r="I31" s="0">
-        <v>2.1289279015366276</v>
+        <v>2.2768105941693797</v>
       </c>
       <c r="J31" s="0">
-        <v>2.1289279015366276</v>
+        <v>2.2768105941693797</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>656.11270000000002</v>
+        <v>669.30840000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.568814959758797</v>
+        <v>21.892168295647078</v>
       </c>
       <c r="F32" s="0">
-        <v>2.0688149597587966</v>
+        <v>2.3921682956470782</v>
       </c>
       <c r="G32" s="0">
-        <v>2.0688149597587966</v>
+        <v>2.3921682956470782</v>
       </c>
       <c r="H32" s="0">
-        <v>21.068814959758797</v>
+        <v>21.392168295647078</v>
       </c>
       <c r="I32" s="0">
-        <v>1.5688149597587966</v>
+        <v>1.8921682956470782</v>
       </c>
       <c r="J32" s="0">
-        <v>1.5688149597587966</v>
+        <v>1.8921682956470782</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,31 +1854,31 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>679.53120000000001</v>
+        <v>712.56219999999996</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.095183860545955</v>
+        <v>21.772544807934413</v>
       </c>
       <c r="F33" s="0">
-        <v>0.095183860545954957</v>
+        <v>0.7725448079344126</v>
       </c>
       <c r="G33" s="0">
-        <v>0.095183860545954957</v>
+        <v>0.7725448079344126</v>
       </c>
       <c r="H33" s="0">
-        <v>20.595183860545955</v>
+        <v>21.272544807934413</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.40481613945404504</v>
+        <v>0.2725448079344126</v>
       </c>
       <c r="J33" s="0">
-        <v>0.40481613945404504</v>
+        <v>0.2725448079344126</v>
       </c>
       <c r="K33" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="0">
         <v>1</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>611.39670000000001</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.039317438301705</v>
+        <v>20.062889116417018</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.21068256169829525</v>
+        <v>-0.18711088358298156</v>
       </c>
       <c r="G34" s="0">
-        <v>0.21068256169829525</v>
+        <v>0.18711088358298156</v>
       </c>
       <c r="H34" s="0">
-        <v>19.539317438301705</v>
+        <v>19.562889116417018</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.71068256169829525</v>
+        <v>-0.68711088358298156</v>
       </c>
       <c r="J34" s="0">
-        <v>0.71068256169829525</v>
+        <v>0.68711088358298156</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>622.68050000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.185278042089109</v>
+        <v>20.168141005576381</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.3147219579108906</v>
+        <v>-1.3318589944236194</v>
       </c>
       <c r="G35" s="0">
-        <v>1.3147219579108906</v>
+        <v>1.3318589944236194</v>
       </c>
       <c r="H35" s="0">
-        <v>19.685278042089109</v>
+        <v>19.668141005576381</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.8147219579108906</v>
+        <v>-1.8318589944236194</v>
       </c>
       <c r="J35" s="0">
-        <v>1.8147219579108906</v>
+        <v>1.8318589944236194</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>601.95100000000002</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>19.825341242237435</v>
+        <v>19.931520368405277</v>
       </c>
       <c r="F36" s="0">
-        <v>0.32534124223743533</v>
+        <v>0.43152036840527686</v>
       </c>
       <c r="G36" s="0">
-        <v>0.32534124223743533</v>
+        <v>0.43152036840527686</v>
       </c>
       <c r="H36" s="0">
-        <v>19.325341242237435</v>
+        <v>19.431520368405277</v>
       </c>
       <c r="I36" s="0">
-        <v>-0.17465875776256468</v>
+        <v>-0.068479631594723145</v>
       </c>
       <c r="J36" s="0">
-        <v>0.17465875776256468</v>
+        <v>0.068479631594723145</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>0</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>726.80799999999999</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.368030410186361</v>
+        <v>22.351664824602285</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.6319695898136395</v>
+        <v>-2.6483351753977153</v>
       </c>
       <c r="G37" s="0">
-        <v>2.6319695898136395</v>
+        <v>2.6483351753977153</v>
       </c>
       <c r="H37" s="0">
-        <v>21.868030410186361</v>
+        <v>21.851664824602285</v>
       </c>
       <c r="I37" s="0">
-        <v>-3.1319695898136395</v>
+        <v>-3.1483351753977153</v>
       </c>
       <c r="J37" s="0">
-        <v>3.1319695898136395</v>
+        <v>3.1483351753977153</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>599.73789999999997</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.85940516844218</v>
+        <v>19.790675677758109</v>
       </c>
       <c r="F38" s="0">
-        <v>0.85940516844217996</v>
+        <v>0.79067567775810943</v>
       </c>
       <c r="G38" s="0">
-        <v>0.85940516844217996</v>
+        <v>0.79067567775810943</v>
       </c>
       <c r="H38" s="0">
-        <v>19.35940516844218</v>
+        <v>19.290675677758109</v>
       </c>
       <c r="I38" s="0">
-        <v>0.35940516844217996</v>
+        <v>0.29067567775810943</v>
       </c>
       <c r="J38" s="0">
-        <v>0.35940516844217996</v>
+        <v>0.29067567775810943</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>700.04589999999996</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>21.852541342380043</v>
+        <v>21.848173373042471</v>
       </c>
       <c r="F39" s="0">
-        <v>2.852541342380043</v>
+        <v>2.8481733730424708</v>
       </c>
       <c r="G39" s="0">
-        <v>2.852541342380043</v>
+        <v>2.8481733730424708</v>
       </c>
       <c r="H39" s="0">
-        <v>21.352541342380043</v>
+        <v>21.348173373042471</v>
       </c>
       <c r="I39" s="0">
-        <v>2.352541342380043</v>
+        <v>2.3481733730424708</v>
       </c>
       <c r="J39" s="0">
-        <v>2.352541342380043</v>
+        <v>2.3481733730424708</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>777.77840000000003</v>
+        <v>776.98199999999997</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>23.934419667301277</v>
+        <v>24.039926268792488</v>
       </c>
       <c r="F40" s="0">
-        <v>2.9344196673012775</v>
+        <v>3.0399262687924882</v>
       </c>
       <c r="G40" s="0">
-        <v>2.9344196673012775</v>
+        <v>3.0399262687924882</v>
       </c>
       <c r="H40" s="0">
-        <v>23.434419667301277</v>
+        <v>23.539926268792488</v>
       </c>
       <c r="I40" s="0">
-        <v>2.4344196673012775</v>
+        <v>2.5399262687924882</v>
       </c>
       <c r="J40" s="0">
-        <v>2.4344196673012775</v>
+        <v>2.5399262687924882</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>673.32410000000004</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.166977487799152</v>
+        <v>21.216099451964507</v>
       </c>
       <c r="F41" s="0">
-        <v>0.66697748779915145</v>
+        <v>0.71609945196450653</v>
       </c>
       <c r="G41" s="0">
-        <v>0.66697748779915145</v>
+        <v>0.71609945196450653</v>
       </c>
       <c r="H41" s="0">
-        <v>20.666977487799152</v>
+        <v>20.716099451964507</v>
       </c>
       <c r="I41" s="0">
-        <v>0.16697748779915145</v>
+        <v>0.21609945196450653</v>
       </c>
       <c r="J41" s="0">
-        <v>0.16697748779915145</v>
+        <v>0.21609945196450653</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>518.52380000000005</v>
+        <v>526.36469999999997</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.08838689112309</v>
+        <v>19.125495023825913</v>
       </c>
       <c r="F42" s="0">
-        <v>-0.16161310887691016</v>
+        <v>-0.12450497617408729</v>
       </c>
       <c r="G42" s="0">
-        <v>0.16161310887691016</v>
+        <v>0.12450497617408729</v>
       </c>
       <c r="H42" s="0">
-        <v>18.58838689112309</v>
+        <v>18.625495023825913</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.66161310887691016</v>
+        <v>-0.62450497617408729</v>
       </c>
       <c r="J42" s="0">
-        <v>0.66161310887691016</v>
+        <v>0.62450497617408729</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>586.85530000000006</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.657159449161441</v>
+        <v>19.656871417275362</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.34284055083855947</v>
+        <v>-0.34312858272463842</v>
       </c>
       <c r="G43" s="0">
-        <v>0.34284055083855947</v>
+        <v>0.34312858272463842</v>
       </c>
       <c r="H43" s="0">
-        <v>19.157159449161441</v>
+        <v>19.156871417275362</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.84284055083855947</v>
+        <v>-0.84312858272463842</v>
       </c>
       <c r="J43" s="0">
-        <v>0.84284055083855947</v>
+        <v>0.84312858272463842</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>663.21749999999997</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.447751847161587</v>
+        <v>21.478554937939656</v>
       </c>
       <c r="F44" s="0">
-        <v>1.4477518471615873</v>
+        <v>1.4785549379396557</v>
       </c>
       <c r="G44" s="0">
-        <v>1.4477518471615873</v>
+        <v>1.4785549379396557</v>
       </c>
       <c r="H44" s="0">
-        <v>20.947751847161587</v>
+        <v>20.978554937939656</v>
       </c>
       <c r="I44" s="0">
-        <v>0.94775184716158734</v>
+        <v>0.97855493793965565</v>
       </c>
       <c r="J44" s="0">
-        <v>0.94775184716158734</v>
+        <v>0.97855493793965565</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>582.90459999999996</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.778732346749994</v>
+        <v>19.75316657903241</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.22126765325000619</v>
+        <v>-0.2468334209675902</v>
       </c>
       <c r="G45" s="0">
-        <v>0.22126765325000619</v>
+        <v>0.2468334209675902</v>
       </c>
       <c r="H45" s="0">
-        <v>19.278732346749994</v>
+        <v>19.25316657903241</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.72126765325000619</v>
+        <v>-0.7468334209675902</v>
       </c>
       <c r="J45" s="0">
-        <v>0.72126765325000619</v>
+        <v>0.7468334209675902</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>728.66980000000001</v>
+        <v>732.64890000000003</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>21.897857095526248</v>
+        <v>21.878238758145834</v>
       </c>
       <c r="F46" s="0">
-        <v>-0.10214290447375163</v>
+        <v>-0.12176124185416626</v>
       </c>
       <c r="G46" s="0">
-        <v>0.10214290447375163</v>
+        <v>0.12176124185416626</v>
       </c>
       <c r="H46" s="0">
-        <v>21.397857095526248</v>
+        <v>21.378238758145834</v>
       </c>
       <c r="I46" s="0">
-        <v>-0.60214290447375163</v>
+        <v>-0.62176124185416626</v>
       </c>
       <c r="J46" s="0">
-        <v>0.60214290447375163</v>
+        <v>0.62176124185416626</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2470,28 +2470,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>697.34799999999996</v>
+        <v>704.21619999999996</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>21.874367727611055</v>
+        <v>21.86446729513683</v>
       </c>
       <c r="F47" s="0">
-        <v>-0.1256322723889447</v>
+        <v>-0.13553270486317004</v>
       </c>
       <c r="G47" s="0">
-        <v>0.1256322723889447</v>
+        <v>0.13553270486317004</v>
       </c>
       <c r="H47" s="0">
-        <v>21.374367727611055</v>
+        <v>21.36446729513683</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.6256322723889447</v>
+        <v>-0.63553270486317004</v>
       </c>
       <c r="J47" s="0">
-        <v>0.6256322723889447</v>
+        <v>0.63553270486317004</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>696.77610000000004</v>
+        <v>707.67989999999998</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.445838037565153</v>
+        <v>21.663497651550191</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.5541619624348471</v>
+        <v>-1.3365023484498089</v>
       </c>
       <c r="G48" s="0">
-        <v>1.5541619624348471</v>
+        <v>1.3365023484498089</v>
       </c>
       <c r="H48" s="0">
-        <v>20.945838037565153</v>
+        <v>21.163497651550191</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.0541619624348471</v>
+        <v>-1.8365023484498089</v>
       </c>
       <c r="J48" s="0">
-        <v>2.0541619624348471</v>
+        <v>1.8365023484498089</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>664.47260000000006</v>
+        <v>666.81700000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.815066628931383</v>
+        <v>20.839685870632426</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.93493337106861674</v>
+        <v>-0.91031412936757405</v>
       </c>
       <c r="G49" s="0">
-        <v>0.93493337106861674</v>
+        <v>0.91031412936757405</v>
       </c>
       <c r="H49" s="0">
-        <v>20.315066628931383</v>
+        <v>20.339685870632426</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.4349333710686167</v>
+        <v>-1.4103141293675741</v>
       </c>
       <c r="J49" s="0">
-        <v>1.4349333710686167</v>
+        <v>1.4103141293675741</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>686.67639999999995</v>
+        <v>688.77390000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.536250606456406</v>
+        <v>21.415338037677536</v>
       </c>
       <c r="F50" s="0">
-        <v>0.036250606456405876</v>
+        <v>-0.084661962322464035</v>
       </c>
       <c r="G50" s="0">
-        <v>0.036250606456405876</v>
+        <v>0.084661962322464035</v>
       </c>
       <c r="H50" s="0">
-        <v>21.036250606456406</v>
+        <v>20.915338037677536</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.46374939354359412</v>
+        <v>-0.58466196232246403</v>
       </c>
       <c r="J50" s="0">
-        <v>0.46374939354359412</v>
+        <v>0.58466196232246403</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>616.17359999999997</v>
+        <v>615.82560000000001</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.174577652957982</v>
+        <v>20.07513777182276</v>
       </c>
       <c r="F51" s="0">
-        <v>0.97457765295798282</v>
+        <v>0.87513777182276087</v>
       </c>
       <c r="G51" s="0">
-        <v>0.97457765295798282</v>
+        <v>0.87513777182276087</v>
       </c>
       <c r="H51" s="0">
-        <v>19.674577652957982</v>
+        <v>19.57513777182276</v>
       </c>
       <c r="I51" s="0">
-        <v>0.47457765295798282</v>
+        <v>0.37513777182276087</v>
       </c>
       <c r="J51" s="0">
-        <v>0.47457765295798282</v>
+        <v>0.37513777182276087</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>575.9733</v>
+        <v>568.91740000000004</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.705574505605288</v>
+        <v>19.643158755801309</v>
       </c>
       <c r="F52" s="0">
-        <v>2.2055745056052878</v>
+        <v>2.1431587558013092</v>
       </c>
       <c r="G52" s="0">
-        <v>2.2055745056052878</v>
+        <v>2.1431587558013092</v>
       </c>
       <c r="H52" s="0">
-        <v>19.205574505605288</v>
+        <v>19.143158755801309</v>
       </c>
       <c r="I52" s="0">
-        <v>1.7055745056052878</v>
+        <v>1.6431587558013092</v>
       </c>
       <c r="J52" s="0">
-        <v>1.7055745056052878</v>
+        <v>1.6431587558013092</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>589.5335</v>
+        <v>594.03499999999997</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.962098128182291</v>
+        <v>19.973038135368597</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5620981281822921</v>
+        <v>1.5730381353685985</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5620981281822921</v>
+        <v>1.5730381353685985</v>
       </c>
       <c r="H53" s="0">
-        <v>19.462098128182291</v>
+        <v>19.473038135368597</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0620981281822921</v>
+        <v>1.0730381353685985</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0620981281822921</v>
+        <v>1.0730381353685985</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,28 +2778,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>563.72389999999996</v>
+        <v>566.51940000000002</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.482416939182603</v>
+        <v>19.487976140782116</v>
       </c>
       <c r="F54" s="0">
-        <v>0.48241693918260253</v>
+        <v>0.48797614078211637</v>
       </c>
       <c r="G54" s="0">
-        <v>0.48241693918260253</v>
+        <v>0.48797614078211637</v>
       </c>
       <c r="H54" s="0">
-        <v>18.982416939182603</v>
+        <v>18.987976140782116</v>
       </c>
       <c r="I54" s="0">
-        <v>-0.017583060817397467</v>
+        <v>-0.012023859217883626</v>
       </c>
       <c r="J54" s="0">
-        <v>0.017583060817397467</v>
+        <v>0.012023859217883626</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>0</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>614.26739999999995</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>19.864401042261648</v>
+        <v>19.970233112710094</v>
       </c>
       <c r="F55" s="0">
-        <v>0.36440104226164749</v>
+        <v>0.47023311271009405</v>
       </c>
       <c r="G55" s="0">
-        <v>0.36440104226164749</v>
+        <v>0.47023311271009405</v>
       </c>
       <c r="H55" s="0">
-        <v>19.364401042261648</v>
+        <v>19.470233112710094</v>
       </c>
       <c r="I55" s="0">
-        <v>-0.13559895773835251</v>
+        <v>-0.029766887289905952</v>
       </c>
       <c r="J55" s="0">
-        <v>0.13559895773835251</v>
+        <v>0.029766887289905952</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>0</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>717.47789999999998</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>21.899393084786141</v>
+        <v>21.889788030866132</v>
       </c>
       <c r="F56" s="0">
-        <v>1.3993930847861407</v>
+        <v>1.3897880308661321</v>
       </c>
       <c r="G56" s="0">
-        <v>1.3993930847861407</v>
+        <v>1.3897880308661321</v>
       </c>
       <c r="H56" s="0">
-        <v>21.399393084786141</v>
+        <v>21.389788030866132</v>
       </c>
       <c r="I56" s="0">
-        <v>0.89939308478614066</v>
+        <v>0.88978803086613212</v>
       </c>
       <c r="J56" s="0">
-        <v>0.89939308478614066</v>
+        <v>0.88978803086613212</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>656.12369999999999</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.955259418235929</v>
+        <v>21.155029550704263</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.044740581764070697</v>
+        <v>0.15502955070426339</v>
       </c>
       <c r="G57" s="0">
-        <v>0.044740581764070697</v>
+        <v>0.15502955070426339</v>
       </c>
       <c r="H57" s="0">
-        <v>20.455259418235929</v>
+        <v>20.655029550704263</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.5447405817640707</v>
+        <v>-0.34497044929573662</v>
       </c>
       <c r="J57" s="0">
-        <v>0.5447405817640707</v>
+        <v>0.34497044929573662</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>730.19860000000006</v>
+        <v>713.17060000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>22.460792818284311</v>
+        <v>22.096594463126639</v>
       </c>
       <c r="F58" s="0">
-        <v>-1.0392071817156889</v>
+        <v>-1.4034055368733611</v>
       </c>
       <c r="G58" s="0">
-        <v>1.0392071817156889</v>
+        <v>1.4034055368733611</v>
       </c>
       <c r="H58" s="0">
-        <v>21.960792818284311</v>
+        <v>21.596594463126639</v>
       </c>
       <c r="I58" s="0">
-        <v>-1.5392071817156889</v>
+        <v>-1.9034055368733611</v>
       </c>
       <c r="J58" s="0">
-        <v>1.5392071817156889</v>
+        <v>1.9034055368733611</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,28 +2998,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>675.12120000000004</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.8069200529889</v>
+        <v>22.049963479530014</v>
       </c>
       <c r="F59" s="0">
-        <v>1.3069200529889002</v>
+        <v>1.5499634795300139</v>
       </c>
       <c r="G59" s="0">
-        <v>1.3069200529889002</v>
+        <v>1.5499634795300139</v>
       </c>
       <c r="H59" s="0">
-        <v>21.3069200529889</v>
+        <v>21.549963479530014</v>
       </c>
       <c r="I59" s="0">
-        <v>0.80692005298890024</v>
+        <v>1.0499634795300139</v>
       </c>
       <c r="J59" s="0">
-        <v>0.80692005298890024</v>
+        <v>1.0499634795300139</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>689.68129999999997</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.935400622966881</v>
+        <v>21.771870365289704</v>
       </c>
       <c r="F60" s="0">
-        <v>0.4354006229668812</v>
+        <v>0.2718703652897041</v>
       </c>
       <c r="G60" s="0">
-        <v>0.4354006229668812</v>
+        <v>0.2718703652897041</v>
       </c>
       <c r="H60" s="0">
-        <v>21.435400622966881</v>
+        <v>21.271870365289704</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.064599377033118799</v>
+        <v>-0.2281296347102959</v>
       </c>
       <c r="J60" s="0">
-        <v>0.064599377033118799</v>
+        <v>0.2281296347102959</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>646.9873</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.79326180989634</v>
+        <v>20.854606866038207</v>
       </c>
       <c r="F61" s="0">
-        <v>0.79326180989633954</v>
+        <v>0.8546068660382069</v>
       </c>
       <c r="G61" s="0">
-        <v>0.79326180989633954</v>
+        <v>0.8546068660382069</v>
       </c>
       <c r="H61" s="0">
-        <v>20.29326180989634</v>
+        <v>20.354606866038207</v>
       </c>
       <c r="I61" s="0">
-        <v>0.29326180989633954</v>
+        <v>0.3546068660382069</v>
       </c>
       <c r="J61" s="0">
-        <v>0.29326180989633954</v>
+        <v>0.3546068660382069</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>680.14350000000002</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.899870733325191</v>
+        <v>21.469561132632521</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.1001292666748093</v>
+        <v>-1.5304388673674794</v>
       </c>
       <c r="G62" s="0">
-        <v>1.1001292666748093</v>
+        <v>1.5304388673674794</v>
       </c>
       <c r="H62" s="0">
-        <v>21.399870733325191</v>
+        <v>20.969561132632521</v>
       </c>
       <c r="I62" s="0">
-        <v>-1.6001292666748093</v>
+        <v>-2.0304388673674794</v>
       </c>
       <c r="J62" s="0">
-        <v>1.6001292666748093</v>
+        <v>2.0304388673674794</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>675.0444</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.679222579058358</v>
+        <v>21.347904237482851</v>
       </c>
       <c r="F63" s="0">
-        <v>0.17922257905835792</v>
+        <v>-0.15209576251714907</v>
       </c>
       <c r="G63" s="0">
-        <v>0.17922257905835792</v>
+        <v>0.15209576251714907</v>
       </c>
       <c r="H63" s="0">
-        <v>21.179222579058358</v>
+        <v>20.847904237482851</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.32077742094164208</v>
+        <v>-0.65209576251714907</v>
       </c>
       <c r="J63" s="0">
-        <v>0.32077742094164208</v>
+        <v>0.65209576251714907</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>635.10969999999998</v>
+        <v>638.85119999999995</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.40316331714093</v>
+        <v>20.350601066085769</v>
       </c>
       <c r="F64" s="0">
-        <v>-2.0968366828590703</v>
+        <v>-2.149398933914231</v>
       </c>
       <c r="G64" s="0">
-        <v>2.0968366828590703</v>
+        <v>2.149398933914231</v>
       </c>
       <c r="H64" s="0">
-        <v>19.90316331714093</v>
+        <v>19.850601066085769</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.5968366828590703</v>
+        <v>-2.649398933914231</v>
       </c>
       <c r="J64" s="0">
-        <v>2.5968366828590703</v>
+        <v>2.649398933914231</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>595.31380000000001</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>20.277776955137607</v>
+        <v>20.235533833101588</v>
       </c>
       <c r="F65" s="0">
-        <v>1.0277769551376075</v>
+        <v>0.98553383310158793</v>
       </c>
       <c r="G65" s="0">
-        <v>1.0277769551376075</v>
+        <v>0.98553383310158793</v>
       </c>
       <c r="H65" s="0">
-        <v>19.777776955137607</v>
+        <v>19.735533833101588</v>
       </c>
       <c r="I65" s="0">
-        <v>0.52777695513760747</v>
+        <v>0.48553383310158793</v>
       </c>
       <c r="J65" s="0">
-        <v>0.52777695513760747</v>
+        <v>0.48553383310158793</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>698.0498</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>20.969006578114911</v>
+        <v>21.454144701031019</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.5309934218850891</v>
+        <v>-2.0458552989689807</v>
       </c>
       <c r="G66" s="0">
-        <v>2.5309934218850891</v>
+        <v>2.0458552989689807</v>
       </c>
       <c r="H66" s="0">
-        <v>20.469006578114911</v>
+        <v>20.954144701031019</v>
       </c>
       <c r="I66" s="0">
-        <v>-3.0309934218850891</v>
+        <v>-2.5458552989689807</v>
       </c>
       <c r="J66" s="0">
-        <v>3.0309934218850891</v>
+        <v>2.5458552989689807</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>634.08339999999998</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.37857307302712</v>
+        <v>20.319062615765738</v>
       </c>
       <c r="F67" s="0">
-        <v>-1.1214269269728803</v>
+        <v>-1.1809373842342623</v>
       </c>
       <c r="G67" s="0">
-        <v>1.1214269269728803</v>
+        <v>1.1809373842342623</v>
       </c>
       <c r="H67" s="0">
-        <v>19.87857307302712</v>
+        <v>19.819062615765738</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.6214269269728803</v>
+        <v>-1.6809373842342623</v>
       </c>
       <c r="J67" s="0">
-        <v>1.6214269269728803</v>
+        <v>1.6809373842342623</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>572.66319999999996</v>
+        <v>578.7296</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>19.867879334065755</v>
+        <v>19.924030575958984</v>
       </c>
       <c r="F68" s="0">
-        <v>0.8678793340657549</v>
+        <v>0.92403057595898375</v>
       </c>
       <c r="G68" s="0">
-        <v>0.8678793340657549</v>
+        <v>0.92403057595898375</v>
       </c>
       <c r="H68" s="0">
-        <v>19.367879334065755</v>
+        <v>19.424030575958984</v>
       </c>
       <c r="I68" s="0">
-        <v>0.3678793340657549</v>
+        <v>0.42403057595898375</v>
       </c>
       <c r="J68" s="0">
-        <v>0.3678793340657549</v>
+        <v>0.42403057595898375</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3476,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.1539999999999999</v>
+        <v>1.1910000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.476</v>
+        <v>1.4890000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>0.32200000000000001</v>
+        <v>0.312</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.060999999999999999</v>
+        <v>-0.062</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3495,16 +3495,16 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C3" s="0">
         <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E3" s="0">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.204</v>
+        <v>1.236</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.56100000000000006</v>
+        <v>-0.56200000000000006</v>
       </c>
       <c r="F5" s="0">
-        <v>56.700000000000003</v>
+        <v>49.299999999999997</v>
       </c>
       <c r="G5" s="0">
-        <v>36</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="6">
@@ -3548,16 +3548,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.1479999999999999</v>
+        <v>1.184</v>
       </c>
       <c r="C6" s="0">
-        <v>1.4219999999999999</v>
+        <v>1.4410000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>0.36799999999999999</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="E6" s="0">
-        <v>0</v>
+        <v>-0.0040000000000000001</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3567,18 +3567,18 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.161</v>
+        <v>1.196</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.5</v>
+        <v>-0.504</v>
       </c>
       <c r="F7" s="0">
-        <v>52.200000000000003</v>
+        <v>47.799999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>32.799999999999997</v>
+        <v>40.299999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>9.0949000000000009</v>
+        <v>8.9078999999999997</v>
       </c>
       <c r="C2" s="0">
-        <v>1.6456</v>
+        <v>1.6880999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>5.5270000000000001</v>
+        <v>5.2770000000000001</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="0">
-        <v>0.018200000000000001</v>
+        <v>0.0184</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025000000000000001</v>
+        <v>0.0025999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>7.1900000000000004</v>
+        <v>7.1180000000000003</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>0.29480000000000001</v>
+        <v>0.3347</v>
       </c>
       <c r="C4" s="0">
-        <v>0.33589999999999998</v>
+        <v>0.3372</v>
       </c>
       <c r="D4" s="0">
-        <v>0.878</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="E4" s="0">
-        <v>0.38350000000000001</v>
+        <v>0.32469999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化_性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化_性別.xlsx
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>606.4973</v>
+        <v>610.42669999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.048176298852031</v>
+        <v>20.023165663387591</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.9518237011479691</v>
+        <v>-2.9768343366124093</v>
       </c>
       <c r="G2" s="0">
-        <v>2.9518237011479691</v>
+        <v>2.9768343366124093</v>
       </c>
       <c r="H2" s="0">
-        <v>19.548176298852031</v>
+        <v>19.523165663387591</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.4518237011479691</v>
+        <v>-3.4768343366124093</v>
       </c>
       <c r="J2" s="0">
-        <v>3.4518237011479691</v>
+        <v>3.4768343366124093</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>609.20730000000003</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>19.974728939315419</v>
+        <v>20.091838035421716</v>
       </c>
       <c r="F3" s="0">
-        <v>-1.025271060684581</v>
+        <v>-0.90816196457828369</v>
       </c>
       <c r="G3" s="0">
-        <v>1.025271060684581</v>
+        <v>0.90816196457828369</v>
       </c>
       <c r="H3" s="0">
-        <v>19.474728939315419</v>
+        <v>19.591838035421716</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.525271060684581</v>
+        <v>-1.4081619645782837</v>
       </c>
       <c r="J3" s="0">
-        <v>1.525271060684581</v>
+        <v>1.4081619645782837</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>755.06500000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>22.859785352621877</v>
+        <v>23.106264520540172</v>
       </c>
       <c r="F4" s="0">
-        <v>-0.64021464737812295</v>
+        <v>-0.39373547945982779</v>
       </c>
       <c r="G4" s="0">
-        <v>0.64021464737812295</v>
+        <v>0.39373547945982779</v>
       </c>
       <c r="H4" s="0">
-        <v>22.359785352621877</v>
+        <v>22.606264520540172</v>
       </c>
       <c r="I4" s="0">
-        <v>-1.1402146473781229</v>
+        <v>-0.89373547945982779</v>
       </c>
       <c r="J4" s="0">
-        <v>1.1402146473781229</v>
+        <v>0.89373547945982779</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.86080000000004</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.593311171530807</v>
+        <v>19.676050178863164</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.4066888284691928</v>
+        <v>-1.3239498211368357</v>
       </c>
       <c r="G5" s="0">
-        <v>1.4066888284691928</v>
+        <v>1.3239498211368357</v>
       </c>
       <c r="H5" s="0">
-        <v>19.093311171530807</v>
+        <v>19.176050178863164</v>
       </c>
       <c r="I5" s="0">
-        <v>-1.9066888284691927</v>
+        <v>-1.8239498211368357</v>
       </c>
       <c r="J5" s="0">
-        <v>1.9066888284691927</v>
+        <v>1.8239498211368357</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>634.26990000000001</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>20.388254158856995</v>
+        <v>20.332498740551692</v>
       </c>
       <c r="F6" s="0">
-        <v>-1.111745841143005</v>
+        <v>-1.1675012594483078</v>
       </c>
       <c r="G6" s="0">
-        <v>1.111745841143005</v>
+        <v>1.1675012594483078</v>
       </c>
       <c r="H6" s="0">
-        <v>19.888254158856995</v>
+        <v>19.832498740551692</v>
       </c>
       <c r="I6" s="0">
-        <v>-1.611745841143005</v>
+        <v>-1.6675012594483078</v>
       </c>
       <c r="J6" s="0">
-        <v>1.611745841143005</v>
+        <v>1.6675012594483078</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>691.86599999999999</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.491383651673878</v>
+        <v>22.099102765470189</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.50861634832612168</v>
+        <v>0.099102765470188814</v>
       </c>
       <c r="G7" s="0">
-        <v>0.50861634832612168</v>
+        <v>0.099102765470188814</v>
       </c>
       <c r="H7" s="0">
-        <v>20.991383651673878</v>
+        <v>21.599102765470189</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.0086163483261217</v>
+        <v>-0.40089723452981119</v>
       </c>
       <c r="J7" s="0">
-        <v>1.0086163483261217</v>
+        <v>0.40089723452981119</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>763.82230000000004</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.615800372754976</v>
+        <v>24.143395130171186</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.3841996272450245</v>
+        <v>-0.85660486982881423</v>
       </c>
       <c r="G8" s="0">
-        <v>1.3841996272450245</v>
+        <v>0.85660486982881423</v>
       </c>
       <c r="H8" s="0">
-        <v>23.115800372754976</v>
+        <v>23.643395130171186</v>
       </c>
       <c r="I8" s="0">
-        <v>-1.8841996272450246</v>
+        <v>-1.3566048698288142</v>
       </c>
       <c r="J8" s="0">
-        <v>1.8841996272450246</v>
+        <v>1.3566048698288142</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>612.55169999999998</v>
+        <v>584.5915</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.55294803455314</v>
+        <v>19.985766150360345</v>
       </c>
       <c r="F9" s="0">
-        <v>0.052948034553139678</v>
+        <v>-0.51423384963965546</v>
       </c>
       <c r="G9" s="0">
-        <v>0.052948034553139678</v>
+        <v>0.51423384963965546</v>
       </c>
       <c r="H9" s="0">
-        <v>20.05294803455314</v>
+        <v>19.485766150360345</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.44705196544686032</v>
+        <v>-1.0142338496396555</v>
       </c>
       <c r="J9" s="0">
-        <v>0.44705196544686032</v>
+        <v>1.0142338496396555</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>647.83249999999998</v>
+        <v>648.39279999999997</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.337387636050501</v>
+        <v>21.22109388349406</v>
       </c>
       <c r="F10" s="0">
-        <v>0.33738763605050082</v>
+        <v>0.2210938834940599</v>
       </c>
       <c r="G10" s="0">
-        <v>0.33738763605050082</v>
+        <v>0.2210938834940599</v>
       </c>
       <c r="H10" s="0">
-        <v>20.837387636050501</v>
+        <v>20.72109388349406</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.16261236394949918</v>
+        <v>-0.2789061165059401</v>
       </c>
       <c r="J10" s="0">
-        <v>0.16261236394949918</v>
+        <v>0.2789061165059401</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>468.75369999999998</v>
+        <v>466.6764</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.124147908288165</v>
+        <v>19.331317384493403</v>
       </c>
       <c r="F11" s="0">
-        <v>1.1241479082881654</v>
+        <v>1.3313173844934028</v>
       </c>
       <c r="G11" s="0">
-        <v>1.1241479082881654</v>
+        <v>1.3313173844934028</v>
       </c>
       <c r="H11" s="0">
-        <v>18.624147908288165</v>
+        <v>18.831317384493403</v>
       </c>
       <c r="I11" s="0">
-        <v>0.62414790828816535</v>
+        <v>0.83131738449340276</v>
       </c>
       <c r="J11" s="0">
-        <v>0.62414790828816535</v>
+        <v>0.83131738449340276</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>745.02800000000002</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>21.84476871927604</v>
+        <v>21.876422720054517</v>
       </c>
       <c r="F12" s="0">
-        <v>-3.1552312807239602</v>
+        <v>-3.1235772799454829</v>
       </c>
       <c r="G12" s="0">
-        <v>3.1552312807239602</v>
+        <v>3.1235772799454829</v>
       </c>
       <c r="H12" s="0">
-        <v>21.34476871927604</v>
+        <v>21.376422720054517</v>
       </c>
       <c r="I12" s="0">
-        <v>-3.6552312807239602</v>
+        <v>-3.6235772799454829</v>
       </c>
       <c r="J12" s="0">
-        <v>3.6552312807239602</v>
+        <v>3.6235772799454829</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>674.10310000000004</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.635010193967204</v>
+        <v>21.42227565709085</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.86498980603279563</v>
+        <v>-1.0777243429091499</v>
       </c>
       <c r="G13" s="0">
-        <v>0.86498980603279563</v>
+        <v>1.0777243429091499</v>
       </c>
       <c r="H13" s="0">
-        <v>21.135010193967204</v>
+        <v>20.92227565709085</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.3649898060327956</v>
+        <v>-1.5777243429091499</v>
       </c>
       <c r="J13" s="0">
-        <v>1.3649898060327956</v>
+        <v>1.5777243429091499</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>678.64329999999995</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.441165679712618</v>
+        <v>21.573211329222119</v>
       </c>
       <c r="F14" s="0">
-        <v>0.94116567971261844</v>
+        <v>1.0732113292221186</v>
       </c>
       <c r="G14" s="0">
-        <v>0.94116567971261844</v>
+        <v>1.0732113292221186</v>
       </c>
       <c r="H14" s="0">
-        <v>20.941165679712618</v>
+        <v>21.073211329222119</v>
       </c>
       <c r="I14" s="0">
-        <v>0.44116567971261844</v>
+        <v>0.57321132922211859</v>
       </c>
       <c r="J14" s="0">
-        <v>0.44116567971261844</v>
+        <v>0.57321132922211859</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>588.29200000000003</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>19.878903767386611</v>
+        <v>19.899455477144112</v>
       </c>
       <c r="F15" s="0">
-        <v>0.37890376738661047</v>
+        <v>0.39945547714411234</v>
       </c>
       <c r="G15" s="0">
-        <v>0.37890376738661047</v>
+        <v>0.39945547714411234</v>
       </c>
       <c r="H15" s="0">
-        <v>19.378903767386611</v>
+        <v>19.399455477144112</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.12109623261338953</v>
+        <v>-0.10054452285588766</v>
       </c>
       <c r="J15" s="0">
-        <v>0.12109623261338953</v>
+        <v>0.10054452285588766</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>0</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.86260000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>20.680198895703455</v>
+        <v>20.681922105197803</v>
       </c>
       <c r="F16" s="0">
-        <v>1.1801988957034553</v>
+        <v>1.1819221051978026</v>
       </c>
       <c r="G16" s="0">
-        <v>1.1801988957034553</v>
+        <v>1.1819221051978026</v>
       </c>
       <c r="H16" s="0">
-        <v>20.180198895703455</v>
+        <v>20.181922105197803</v>
       </c>
       <c r="I16" s="0">
-        <v>0.68019889570345526</v>
+        <v>0.68192210519780261</v>
       </c>
       <c r="J16" s="0">
-        <v>0.68019889570345526</v>
+        <v>0.68192210519780261</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>557.87480000000005</v>
+        <v>564.40920000000006</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.481749475778226</v>
+        <v>19.540114403034998</v>
       </c>
       <c r="F17" s="0">
-        <v>0.98174947577822635</v>
+        <v>1.0401144030349982</v>
       </c>
       <c r="G17" s="0">
-        <v>0.98174947577822635</v>
+        <v>1.0401144030349982</v>
       </c>
       <c r="H17" s="0">
-        <v>18.981749475778226</v>
+        <v>19.040114403034998</v>
       </c>
       <c r="I17" s="0">
-        <v>0.48174947577822636</v>
+        <v>0.54011440303499825</v>
       </c>
       <c r="J17" s="0">
-        <v>0.48174947577822636</v>
+        <v>0.54011440303499825</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>734.02059999999995</v>
+        <v>736.66660000000002</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>21.875463014787329</v>
+        <v>21.908799986452891</v>
       </c>
       <c r="F18" s="0">
-        <v>-1.8745369852126714</v>
+        <v>-1.8412000135471089</v>
       </c>
       <c r="G18" s="0">
-        <v>1.8745369852126714</v>
+        <v>1.8412000135471089</v>
       </c>
       <c r="H18" s="0">
-        <v>21.375463014787329</v>
+        <v>21.408799986452891</v>
       </c>
       <c r="I18" s="0">
-        <v>-2.3745369852126714</v>
+        <v>-2.3412000135471089</v>
       </c>
       <c r="J18" s="0">
-        <v>2.3745369852126714</v>
+        <v>2.3412000135471089</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>674.8356</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.98703884767173</v>
+        <v>20.929305063063723</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2629611523282698</v>
+        <v>-1.3206949369362775</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2629611523282698</v>
+        <v>1.3206949369362775</v>
       </c>
       <c r="H19" s="0">
-        <v>20.48703884767173</v>
+        <v>20.429305063063723</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7629611523282698</v>
+        <v>-1.8206949369362775</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7629611523282698</v>
+        <v>1.8206949369362775</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>758.93589999999995</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.426257101586071</v>
+        <v>23.559692676381015</v>
       </c>
       <c r="F20" s="0">
-        <v>-2.0737428984139292</v>
+        <v>-1.9403073236189847</v>
       </c>
       <c r="G20" s="0">
-        <v>2.0737428984139292</v>
+        <v>1.9403073236189847</v>
       </c>
       <c r="H20" s="0">
-        <v>22.926257101586071</v>
+        <v>23.059692676381015</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.5737428984139292</v>
+        <v>-2.4403073236189847</v>
       </c>
       <c r="J20" s="0">
-        <v>2.5737428984139292</v>
+        <v>2.4403073236189847</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>530.03160000000003</v>
+        <v>533.39049999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>17.994687511701528</v>
+        <v>17.997777510015183</v>
       </c>
       <c r="F21" s="0">
-        <v>-4.5053124882984719</v>
+        <v>-4.5022224899848169</v>
       </c>
       <c r="G21" s="0">
-        <v>4.5053124882984719</v>
+        <v>4.5022224899848169</v>
       </c>
       <c r="H21" s="0">
-        <v>17.494687511701528</v>
+        <v>17.497777510015183</v>
       </c>
       <c r="I21" s="0">
-        <v>-5.0053124882984719</v>
+        <v>-5.0022224899848169</v>
       </c>
       <c r="J21" s="0">
-        <v>5.0053124882984719</v>
+        <v>5.0022224899848169</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>619.3691</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.376087491662048</v>
+        <v>20.320470002705644</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.123912508337952</v>
+        <v>-1.179529997294356</v>
       </c>
       <c r="G22" s="0">
-        <v>1.123912508337952</v>
+        <v>1.179529997294356</v>
       </c>
       <c r="H22" s="0">
-        <v>19.876087491662048</v>
+        <v>19.820470002705644</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.623912508337952</v>
+        <v>-1.679529997294356</v>
       </c>
       <c r="J22" s="0">
-        <v>1.623912508337952</v>
+        <v>1.679529997294356</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>681.04340000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.526627645175019</v>
+        <v>21.266599070164784</v>
       </c>
       <c r="F23" s="0">
-        <v>1.5266276451750187</v>
+        <v>1.2665990701647836</v>
       </c>
       <c r="G23" s="0">
-        <v>1.5266276451750187</v>
+        <v>1.2665990701647836</v>
       </c>
       <c r="H23" s="0">
-        <v>21.026627645175019</v>
+        <v>20.766599070164784</v>
       </c>
       <c r="I23" s="0">
-        <v>1.0266276451750187</v>
+        <v>0.76659907016478357</v>
       </c>
       <c r="J23" s="0">
-        <v>1.0266276451750187</v>
+        <v>0.76659907016478357</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>585.4384</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.662705903054089</v>
+        <v>19.640702290355698</v>
       </c>
       <c r="F24" s="0">
-        <v>0.16270590305408916</v>
+        <v>0.14070229035569781</v>
       </c>
       <c r="G24" s="0">
-        <v>0.16270590305408916</v>
+        <v>0.14070229035569781</v>
       </c>
       <c r="H24" s="0">
-        <v>19.162705903054089</v>
+        <v>19.140702290355698</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.33729409694591084</v>
+        <v>-0.35929770964430219</v>
       </c>
       <c r="J24" s="0">
-        <v>0.33729409694591084</v>
+        <v>0.35929770964430219</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>581.173</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.738637137464473</v>
+        <v>19.77188858762441</v>
       </c>
       <c r="F25" s="0">
-        <v>1.2386371374644725</v>
+        <v>1.2718885876244101</v>
       </c>
       <c r="G25" s="0">
-        <v>1.2386371374644725</v>
+        <v>1.2718885876244101</v>
       </c>
       <c r="H25" s="0">
-        <v>19.238637137464473</v>
+        <v>19.27188858762441</v>
       </c>
       <c r="I25" s="0">
-        <v>0.73863713746447246</v>
+        <v>0.77188858762441015</v>
       </c>
       <c r="J25" s="0">
-        <v>0.73863713746447246</v>
+        <v>0.77188858762441015</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>692.99239999999998</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>21.810252713772837</v>
+        <v>21.846821512015861</v>
       </c>
       <c r="F26" s="0">
-        <v>0.56025271377283659</v>
+        <v>0.59682151201586109</v>
       </c>
       <c r="G26" s="0">
-        <v>0.56025271377283659</v>
+        <v>0.59682151201586109</v>
       </c>
       <c r="H26" s="0">
-        <v>21.310252713772837</v>
+        <v>21.346821512015861</v>
       </c>
       <c r="I26" s="0">
-        <v>0.060252713772836586</v>
+        <v>0.096821512015861089</v>
       </c>
       <c r="J26" s="0">
-        <v>0.060252713772836586</v>
+        <v>0.096821512015861089</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>643.06439999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.813139483663658</v>
+        <v>20.80482015295166</v>
       </c>
       <c r="F27" s="0">
-        <v>1.5631394836636581</v>
+        <v>1.5548201529516597</v>
       </c>
       <c r="G27" s="0">
-        <v>1.5631394836636581</v>
+        <v>1.5548201529516597</v>
       </c>
       <c r="H27" s="0">
-        <v>20.313139483663658</v>
+        <v>20.30482015295166</v>
       </c>
       <c r="I27" s="0">
-        <v>1.0631394836636581</v>
+        <v>1.0548201529516597</v>
       </c>
       <c r="J27" s="0">
-        <v>1.0631394836636581</v>
+        <v>1.0548201529516597</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>679.27729999999997</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.187297558968847</v>
+        <v>21.881299601636044</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.56270244103115275</v>
+        <v>0.13129960163604437</v>
       </c>
       <c r="G28" s="0">
-        <v>0.56270244103115275</v>
+        <v>0.13129960163604437</v>
       </c>
       <c r="H28" s="0">
-        <v>20.687297558968847</v>
+        <v>21.381299601636044</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.0627024410311528</v>
+        <v>-0.36870039836395563</v>
       </c>
       <c r="J28" s="0">
-        <v>1.0627024410311528</v>
+        <v>0.36870039836395563</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>531.55600000000004</v>
+        <v>527.93060000000003</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.179552814506863</v>
+        <v>19.127993790415108</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.570447185493137</v>
+        <v>-1.6220062095848924</v>
       </c>
       <c r="G29" s="0">
-        <v>1.570447185493137</v>
+        <v>1.6220062095848924</v>
       </c>
       <c r="H29" s="0">
-        <v>18.679552814506863</v>
+        <v>18.627993790415108</v>
       </c>
       <c r="I29" s="0">
-        <v>-2.070447185493137</v>
+        <v>-2.1220062095848924</v>
       </c>
       <c r="J29" s="0">
-        <v>2.070447185493137</v>
+        <v>2.1220062095848924</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>685.61059999999998</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>22.340707442144783</v>
+        <v>22.342921388764886</v>
       </c>
       <c r="F30" s="0">
-        <v>0.8407074421447831</v>
+        <v>0.84292138876488565</v>
       </c>
       <c r="G30" s="0">
-        <v>0.8407074421447831</v>
+        <v>0.84292138876488565</v>
       </c>
       <c r="H30" s="0">
-        <v>21.840707442144783</v>
+        <v>21.842921388764886</v>
       </c>
       <c r="I30" s="0">
-        <v>0.3407074421447831</v>
+        <v>0.34292138876488565</v>
       </c>
       <c r="J30" s="0">
-        <v>0.3407074421447831</v>
+        <v>0.34292138876488565</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>1</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>683.32539999999995</v>
+        <v>687.38679999999999</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>22.27681059416938</v>
+        <v>22.295617071579485</v>
       </c>
       <c r="F31" s="0">
-        <v>2.7768105941693797</v>
+        <v>2.7956170715794855</v>
       </c>
       <c r="G31" s="0">
-        <v>2.7768105941693797</v>
+        <v>2.7956170715794855</v>
       </c>
       <c r="H31" s="0">
-        <v>21.77681059416938</v>
+        <v>21.795617071579485</v>
       </c>
       <c r="I31" s="0">
-        <v>2.2768105941693797</v>
+        <v>2.2956170715794855</v>
       </c>
       <c r="J31" s="0">
-        <v>2.2768105941693797</v>
+        <v>2.2956170715794855</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>669.30840000000001</v>
+        <v>664.20730000000003</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.892168295647078</v>
+        <v>21.632448174160803</v>
       </c>
       <c r="F32" s="0">
-        <v>2.3921682956470782</v>
+        <v>2.1324481741608032</v>
       </c>
       <c r="G32" s="0">
-        <v>2.3921682956470782</v>
+        <v>2.1324481741608032</v>
       </c>
       <c r="H32" s="0">
-        <v>21.392168295647078</v>
+        <v>21.132448174160803</v>
       </c>
       <c r="I32" s="0">
-        <v>1.8921682956470782</v>
+        <v>1.6324481741608032</v>
       </c>
       <c r="J32" s="0">
-        <v>1.8921682956470782</v>
+        <v>1.6324481741608032</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,31 +1854,31 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>712.56219999999996</v>
+        <v>700.82140000000004</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.772544807934413</v>
+        <v>21.48604745951743</v>
       </c>
       <c r="F33" s="0">
-        <v>0.7725448079344126</v>
+        <v>0.48604745951742956</v>
       </c>
       <c r="G33" s="0">
-        <v>0.7725448079344126</v>
+        <v>0.48604745951742956</v>
       </c>
       <c r="H33" s="0">
-        <v>21.272544807934413</v>
+        <v>20.98604745951743</v>
       </c>
       <c r="I33" s="0">
-        <v>0.2725448079344126</v>
+        <v>-0.013952540482570441</v>
       </c>
       <c r="J33" s="0">
-        <v>0.2725448079344126</v>
+        <v>0.013952540482570441</v>
       </c>
       <c r="K33" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="0">
         <v>1</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.39670000000001</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.062889116417018</v>
+        <v>20.001590070435817</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.18711088358298156</v>
+        <v>-0.24840992956418262</v>
       </c>
       <c r="G34" s="0">
-        <v>0.18711088358298156</v>
+        <v>0.24840992956418262</v>
       </c>
       <c r="H34" s="0">
-        <v>19.562889116417018</v>
+        <v>19.501590070435817</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.68711088358298156</v>
+        <v>-0.74840992956418262</v>
       </c>
       <c r="J34" s="0">
-        <v>0.68711088358298156</v>
+        <v>0.74840992956418262</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>622.68050000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.168141005576381</v>
+        <v>20.08839788158458</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.3318589944236194</v>
+        <v>-1.4116021184154199</v>
       </c>
       <c r="G35" s="0">
-        <v>1.3318589944236194</v>
+        <v>1.4116021184154199</v>
       </c>
       <c r="H35" s="0">
-        <v>19.668141005576381</v>
+        <v>19.58839788158458</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.8318589944236194</v>
+        <v>-1.9116021184154199</v>
       </c>
       <c r="J35" s="0">
-        <v>1.8318589944236194</v>
+        <v>1.9116021184154199</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>601.95100000000002</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>19.931520368405277</v>
+        <v>19.868015352238221</v>
       </c>
       <c r="F36" s="0">
-        <v>0.43152036840527686</v>
+        <v>0.36801535223822057</v>
       </c>
       <c r="G36" s="0">
-        <v>0.43152036840527686</v>
+        <v>0.36801535223822057</v>
       </c>
       <c r="H36" s="0">
-        <v>19.431520368405277</v>
+        <v>19.368015352238221</v>
       </c>
       <c r="I36" s="0">
-        <v>-0.068479631594723145</v>
+        <v>-0.13198464776177943</v>
       </c>
       <c r="J36" s="0">
-        <v>0.068479631594723145</v>
+        <v>0.13198464776177943</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>0</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>726.80799999999999</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.351664824602285</v>
+        <v>22.736544390285076</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.6483351753977153</v>
+        <v>-2.2634556097149243</v>
       </c>
       <c r="G37" s="0">
-        <v>2.6483351753977153</v>
+        <v>2.2634556097149243</v>
       </c>
       <c r="H37" s="0">
-        <v>21.851664824602285</v>
+        <v>22.236544390285076</v>
       </c>
       <c r="I37" s="0">
-        <v>-3.1483351753977153</v>
+        <v>-2.7634556097149243</v>
       </c>
       <c r="J37" s="0">
-        <v>3.1483351753977153</v>
+        <v>2.7634556097149243</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>599.73789999999997</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.790675677758109</v>
+        <v>19.776373538215712</v>
       </c>
       <c r="F38" s="0">
-        <v>0.79067567775810943</v>
+        <v>0.77637353821571153</v>
       </c>
       <c r="G38" s="0">
-        <v>0.79067567775810943</v>
+        <v>0.77637353821571153</v>
       </c>
       <c r="H38" s="0">
-        <v>19.290675677758109</v>
+        <v>19.276373538215712</v>
       </c>
       <c r="I38" s="0">
-        <v>0.29067567775810943</v>
+        <v>0.27637353821571153</v>
       </c>
       <c r="J38" s="0">
-        <v>0.29067567775810943</v>
+        <v>0.27637353821571153</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>700.04589999999996</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>21.848173373042471</v>
+        <v>21.873480892473943</v>
       </c>
       <c r="F39" s="0">
-        <v>2.8481733730424708</v>
+        <v>2.8734808924739426</v>
       </c>
       <c r="G39" s="0">
-        <v>2.8481733730424708</v>
+        <v>2.8734808924739426</v>
       </c>
       <c r="H39" s="0">
-        <v>21.348173373042471</v>
+        <v>21.373480892473943</v>
       </c>
       <c r="I39" s="0">
-        <v>2.3481733730424708</v>
+        <v>2.3734808924739426</v>
       </c>
       <c r="J39" s="0">
-        <v>2.3481733730424708</v>
+        <v>2.3734808924739426</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>776.98199999999997</v>
+        <v>762.38530000000003</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>24.039926268792488</v>
+        <v>23.80517436349313</v>
       </c>
       <c r="F40" s="0">
-        <v>3.0399262687924882</v>
+        <v>2.8051743634931299</v>
       </c>
       <c r="G40" s="0">
-        <v>3.0399262687924882</v>
+        <v>2.8051743634931299</v>
       </c>
       <c r="H40" s="0">
-        <v>23.539926268792488</v>
+        <v>23.30517436349313</v>
       </c>
       <c r="I40" s="0">
-        <v>2.5399262687924882</v>
+        <v>2.3051743634931299</v>
       </c>
       <c r="J40" s="0">
-        <v>2.5399262687924882</v>
+        <v>2.3051743634931299</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>673.32410000000004</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.216099451964507</v>
+        <v>21.174209284602817</v>
       </c>
       <c r="F41" s="0">
-        <v>0.71609945196450653</v>
+        <v>0.67420928460281715</v>
       </c>
       <c r="G41" s="0">
-        <v>0.71609945196450653</v>
+        <v>0.67420928460281715</v>
       </c>
       <c r="H41" s="0">
-        <v>20.716099451964507</v>
+        <v>20.674209284602817</v>
       </c>
       <c r="I41" s="0">
-        <v>0.21609945196450653</v>
+        <v>0.17420928460281715</v>
       </c>
       <c r="J41" s="0">
-        <v>0.21609945196450653</v>
+        <v>0.17420928460281715</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>526.36469999999997</v>
+        <v>523.23350000000005</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.125495023825913</v>
+        <v>19.081898152504159</v>
       </c>
       <c r="F42" s="0">
-        <v>-0.12450497617408729</v>
+        <v>-0.16810184749584067</v>
       </c>
       <c r="G42" s="0">
-        <v>0.12450497617408729</v>
+        <v>0.16810184749584067</v>
       </c>
       <c r="H42" s="0">
-        <v>18.625495023825913</v>
+        <v>18.581898152504159</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.62450497617408729</v>
+        <v>-0.66810184749584067</v>
       </c>
       <c r="J42" s="0">
-        <v>0.62450497617408729</v>
+        <v>0.66810184749584067</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>586.85530000000006</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.656871417275362</v>
+        <v>19.696631912598235</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.34312858272463842</v>
+        <v>-0.3033680874017648</v>
       </c>
       <c r="G43" s="0">
-        <v>0.34312858272463842</v>
+        <v>0.3033680874017648</v>
       </c>
       <c r="H43" s="0">
-        <v>19.156871417275362</v>
+        <v>19.196631912598235</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.84312858272463842</v>
+        <v>-0.8033680874017648</v>
       </c>
       <c r="J43" s="0">
-        <v>0.84312858272463842</v>
+        <v>0.8033680874017648</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>663.21749999999997</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.478554937939656</v>
+        <v>21.456300813039029</v>
       </c>
       <c r="F44" s="0">
-        <v>1.4785549379396557</v>
+        <v>1.4563008130390287</v>
       </c>
       <c r="G44" s="0">
-        <v>1.4785549379396557</v>
+        <v>1.4563008130390287</v>
       </c>
       <c r="H44" s="0">
-        <v>20.978554937939656</v>
+        <v>20.956300813039029</v>
       </c>
       <c r="I44" s="0">
-        <v>0.97855493793965565</v>
+        <v>0.9563008130390287</v>
       </c>
       <c r="J44" s="0">
-        <v>0.97855493793965565</v>
+        <v>0.9563008130390287</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>582.90459999999996</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.75316657903241</v>
+        <v>19.752019619457094</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.2468334209675902</v>
+        <v>-0.24798038054290572</v>
       </c>
       <c r="G45" s="0">
-        <v>0.2468334209675902</v>
+        <v>0.24798038054290572</v>
       </c>
       <c r="H45" s="0">
-        <v>19.25316657903241</v>
+        <v>19.252019619457094</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.7468334209675902</v>
+        <v>-0.74798038054290572</v>
       </c>
       <c r="J45" s="0">
-        <v>0.7468334209675902</v>
+        <v>0.74798038054290572</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>732.64890000000003</v>
+        <v>725.4751</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>21.878238758145834</v>
+        <v>21.925877472858637</v>
       </c>
       <c r="F46" s="0">
-        <v>-0.12176124185416626</v>
+        <v>-0.074122527141362582</v>
       </c>
       <c r="G46" s="0">
-        <v>0.12176124185416626</v>
+        <v>0.074122527141362582</v>
       </c>
       <c r="H46" s="0">
-        <v>21.378238758145834</v>
+        <v>21.425877472858637</v>
       </c>
       <c r="I46" s="0">
-        <v>-0.62176124185416626</v>
+        <v>-0.57412252714136258</v>
       </c>
       <c r="J46" s="0">
-        <v>0.62176124185416626</v>
+        <v>0.57412252714136258</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2470,28 +2470,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>704.21619999999996</v>
+        <v>700.72990000000004</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>21.86446729513683</v>
+        <v>21.88224167673458</v>
       </c>
       <c r="F47" s="0">
-        <v>-0.13553270486317004</v>
+        <v>-0.11775832326542002</v>
       </c>
       <c r="G47" s="0">
-        <v>0.13553270486317004</v>
+        <v>0.11775832326542002</v>
       </c>
       <c r="H47" s="0">
-        <v>21.36446729513683</v>
+        <v>21.38224167673458</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.63553270486317004</v>
+        <v>-0.61775832326542002</v>
       </c>
       <c r="J47" s="0">
-        <v>0.63553270486317004</v>
+        <v>0.61775832326542002</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>707.67989999999998</v>
+        <v>697.40779999999995</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.663497651550191</v>
+        <v>21.40062547142086</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.3365023484498089</v>
+        <v>-1.5993745285791405</v>
       </c>
       <c r="G48" s="0">
-        <v>1.3365023484498089</v>
+        <v>1.5993745285791405</v>
       </c>
       <c r="H48" s="0">
-        <v>21.163497651550191</v>
+        <v>20.90062547142086</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.8365023484498089</v>
+        <v>-2.0993745285791405</v>
       </c>
       <c r="J48" s="0">
-        <v>1.8365023484498089</v>
+        <v>2.0993745285791405</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>666.81700000000001</v>
+        <v>664.56500000000005</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.839685870632426</v>
+        <v>20.697378865296329</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.91031412936757405</v>
+        <v>-1.0526211347036707</v>
       </c>
       <c r="G49" s="0">
-        <v>0.91031412936757405</v>
+        <v>1.0526211347036707</v>
       </c>
       <c r="H49" s="0">
-        <v>20.339685870632426</v>
+        <v>20.197378865296329</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.4103141293675741</v>
+        <v>-1.5526211347036707</v>
       </c>
       <c r="J49" s="0">
-        <v>1.4103141293675741</v>
+        <v>1.5526211347036707</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>688.77390000000003</v>
+        <v>689.15930000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.415338037677536</v>
+        <v>21.433890003280329</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.084661962322464035</v>
+        <v>-0.066109996719671216</v>
       </c>
       <c r="G50" s="0">
-        <v>0.084661962322464035</v>
+        <v>0.066109996719671216</v>
       </c>
       <c r="H50" s="0">
-        <v>20.915338037677536</v>
+        <v>20.933890003280329</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.58466196232246403</v>
+        <v>-0.56610999671967122</v>
       </c>
       <c r="J50" s="0">
-        <v>0.58466196232246403</v>
+        <v>0.56610999671967122</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>615.82560000000001</v>
+        <v>610.64480000000003</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.07513777182276</v>
+        <v>19.970749222394552</v>
       </c>
       <c r="F51" s="0">
-        <v>0.87513777182276087</v>
+        <v>0.7707492223945529</v>
       </c>
       <c r="G51" s="0">
-        <v>0.87513777182276087</v>
+        <v>0.7707492223945529</v>
       </c>
       <c r="H51" s="0">
-        <v>19.57513777182276</v>
+        <v>19.470749222394552</v>
       </c>
       <c r="I51" s="0">
-        <v>0.37513777182276087</v>
+        <v>0.2707492223945529</v>
       </c>
       <c r="J51" s="0">
-        <v>0.37513777182276087</v>
+        <v>0.2707492223945529</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>568.91740000000004</v>
+        <v>576.71630000000005</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.643158755801309</v>
+        <v>19.73451117800656</v>
       </c>
       <c r="F52" s="0">
-        <v>2.1431587558013092</v>
+        <v>2.2345111780065601</v>
       </c>
       <c r="G52" s="0">
-        <v>2.1431587558013092</v>
+        <v>2.2345111780065601</v>
       </c>
       <c r="H52" s="0">
-        <v>19.143158755801309</v>
+        <v>19.23451117800656</v>
       </c>
       <c r="I52" s="0">
-        <v>1.6431587558013092</v>
+        <v>1.7345111780065601</v>
       </c>
       <c r="J52" s="0">
-        <v>1.6431587558013092</v>
+        <v>1.7345111780065601</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>594.03499999999997</v>
+        <v>598.05470000000003</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.973038135368597</v>
+        <v>19.991769599382796</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5730381353685985</v>
+        <v>1.5917695993827969</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5730381353685985</v>
+        <v>1.5917695993827969</v>
       </c>
       <c r="H53" s="0">
-        <v>19.473038135368597</v>
+        <v>19.491769599382796</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0730381353685985</v>
+        <v>1.091769599382797</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0730381353685985</v>
+        <v>1.091769599382797</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,31 +2778,31 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>566.51940000000002</v>
+        <v>573.06939999999997</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.487976140782116</v>
+        <v>19.6098214025731</v>
       </c>
       <c r="F54" s="0">
-        <v>0.48797614078211637</v>
+        <v>0.60982140257310036</v>
       </c>
       <c r="G54" s="0">
-        <v>0.48797614078211637</v>
+        <v>0.60982140257310036</v>
       </c>
       <c r="H54" s="0">
-        <v>18.987976140782116</v>
+        <v>19.1098214025731</v>
       </c>
       <c r="I54" s="0">
-        <v>-0.012023859217883626</v>
+        <v>0.10982140257310036</v>
       </c>
       <c r="J54" s="0">
-        <v>0.012023859217883626</v>
+        <v>0.10982140257310036</v>
       </c>
       <c r="K54" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="0">
         <v>5</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>614.26739999999995</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>19.970233112710094</v>
+        <v>19.924467371175918</v>
       </c>
       <c r="F55" s="0">
-        <v>0.47023311271009405</v>
+        <v>0.42446737117591837</v>
       </c>
       <c r="G55" s="0">
-        <v>0.47023311271009405</v>
+        <v>0.42446737117591837</v>
       </c>
       <c r="H55" s="0">
-        <v>19.470233112710094</v>
+        <v>19.424467371175918</v>
       </c>
       <c r="I55" s="0">
-        <v>-0.029766887289905952</v>
+        <v>-0.075532628824081627</v>
       </c>
       <c r="J55" s="0">
-        <v>0.029766887289905952</v>
+        <v>0.075532628824081627</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>0</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>717.47789999999998</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>21.889788030866132</v>
+        <v>21.883636959135728</v>
       </c>
       <c r="F56" s="0">
-        <v>1.3897880308661321</v>
+        <v>1.3836369591357283</v>
       </c>
       <c r="G56" s="0">
-        <v>1.3897880308661321</v>
+        <v>1.3836369591357283</v>
       </c>
       <c r="H56" s="0">
-        <v>21.389788030866132</v>
+        <v>21.383636959135728</v>
       </c>
       <c r="I56" s="0">
-        <v>0.88978803086613212</v>
+        <v>0.88363695913572826</v>
       </c>
       <c r="J56" s="0">
-        <v>0.88978803086613212</v>
+        <v>0.88363695913572826</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>656.12369999999999</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.155029550704263</v>
+        <v>20.821930963072379</v>
       </c>
       <c r="F57" s="0">
-        <v>0.15502955070426339</v>
+        <v>-0.17806903692762077</v>
       </c>
       <c r="G57" s="0">
-        <v>0.15502955070426339</v>
+        <v>0.17806903692762077</v>
       </c>
       <c r="H57" s="0">
-        <v>20.655029550704263</v>
+        <v>20.321930963072379</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.34497044929573662</v>
+        <v>-0.67806903692762077</v>
       </c>
       <c r="J57" s="0">
-        <v>0.34497044929573662</v>
+        <v>0.67806903692762077</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>713.17060000000004</v>
+        <v>713.38980000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>22.096594463126639</v>
+        <v>22.208342278161283</v>
       </c>
       <c r="F58" s="0">
-        <v>-1.4034055368733611</v>
+        <v>-1.2916577218387175</v>
       </c>
       <c r="G58" s="0">
-        <v>1.4034055368733611</v>
+        <v>1.2916577218387175</v>
       </c>
       <c r="H58" s="0">
-        <v>21.596594463126639</v>
+        <v>21.708342278161283</v>
       </c>
       <c r="I58" s="0">
-        <v>-1.9034055368733611</v>
+        <v>-1.7916577218387175</v>
       </c>
       <c r="J58" s="0">
-        <v>1.9034055368733611</v>
+        <v>1.7916577218387175</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,28 +2998,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>675.12120000000004</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>22.049963479530014</v>
+        <v>21.848799543532266</v>
       </c>
       <c r="F59" s="0">
-        <v>1.5499634795300139</v>
+        <v>1.3487995435322659</v>
       </c>
       <c r="G59" s="0">
-        <v>1.5499634795300139</v>
+        <v>1.3487995435322659</v>
       </c>
       <c r="H59" s="0">
-        <v>21.549963479530014</v>
+        <v>21.348799543532266</v>
       </c>
       <c r="I59" s="0">
-        <v>1.0499634795300139</v>
+        <v>0.84879954353226594</v>
       </c>
       <c r="J59" s="0">
-        <v>1.0499634795300139</v>
+        <v>0.84879954353226594</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>689.68129999999997</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.771870365289704</v>
+        <v>21.958852610853136</v>
       </c>
       <c r="F60" s="0">
-        <v>0.2718703652897041</v>
+        <v>0.45885261085313545</v>
       </c>
       <c r="G60" s="0">
-        <v>0.2718703652897041</v>
+        <v>0.45885261085313545</v>
       </c>
       <c r="H60" s="0">
-        <v>21.271870365289704</v>
+        <v>21.458852610853136</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.2281296347102959</v>
+        <v>-0.041147389146864555</v>
       </c>
       <c r="J60" s="0">
-        <v>0.2281296347102959</v>
+        <v>0.041147389146864555</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>646.9873</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.854606866038207</v>
+        <v>20.886741862335086</v>
       </c>
       <c r="F61" s="0">
-        <v>0.8546068660382069</v>
+        <v>0.88674186233508579</v>
       </c>
       <c r="G61" s="0">
-        <v>0.8546068660382069</v>
+        <v>0.88674186233508579</v>
       </c>
       <c r="H61" s="0">
-        <v>20.354606866038207</v>
+        <v>20.386741862335086</v>
       </c>
       <c r="I61" s="0">
-        <v>0.3546068660382069</v>
+        <v>0.38674186233508578</v>
       </c>
       <c r="J61" s="0">
-        <v>0.3546068660382069</v>
+        <v>0.38674186233508578</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>680.14350000000002</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.469561132632521</v>
+        <v>21.739627764251097</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.5304388673674794</v>
+        <v>-1.2603722357489033</v>
       </c>
       <c r="G62" s="0">
-        <v>1.5304388673674794</v>
+        <v>1.2603722357489033</v>
       </c>
       <c r="H62" s="0">
-        <v>20.969561132632521</v>
+        <v>21.239627764251097</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.0304388673674794</v>
+        <v>-1.7603722357489033</v>
       </c>
       <c r="J62" s="0">
-        <v>2.0304388673674794</v>
+        <v>1.7603722357489033</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>675.0444</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.347904237482851</v>
+        <v>21.23569310744913</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.15209576251714907</v>
+        <v>-0.26430689255087003</v>
       </c>
       <c r="G63" s="0">
-        <v>0.15209576251714907</v>
+        <v>0.26430689255087003</v>
       </c>
       <c r="H63" s="0">
-        <v>20.847904237482851</v>
+        <v>20.73569310744913</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.65209576251714907</v>
+        <v>-0.76430689255087003</v>
       </c>
       <c r="J63" s="0">
-        <v>0.65209576251714907</v>
+        <v>0.76430689255087003</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>638.85119999999995</v>
+        <v>643.54809999999998</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.350601066085769</v>
+        <v>20.395845740611709</v>
       </c>
       <c r="F64" s="0">
-        <v>-2.149398933914231</v>
+        <v>-2.1041542593882916</v>
       </c>
       <c r="G64" s="0">
-        <v>2.149398933914231</v>
+        <v>2.1041542593882916</v>
       </c>
       <c r="H64" s="0">
-        <v>19.850601066085769</v>
+        <v>19.895845740611709</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.649398933914231</v>
+        <v>-2.6041542593882916</v>
       </c>
       <c r="J64" s="0">
-        <v>2.649398933914231</v>
+        <v>2.6041542593882916</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>595.31380000000001</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>20.235533833101588</v>
+        <v>20.1861976329795</v>
       </c>
       <c r="F65" s="0">
-        <v>0.98553383310158793</v>
+        <v>0.93619763297949987</v>
       </c>
       <c r="G65" s="0">
-        <v>0.98553383310158793</v>
+        <v>0.93619763297949987</v>
       </c>
       <c r="H65" s="0">
-        <v>19.735533833101588</v>
+        <v>19.6861976329795</v>
       </c>
       <c r="I65" s="0">
-        <v>0.48553383310158793</v>
+        <v>0.43619763297949987</v>
       </c>
       <c r="J65" s="0">
-        <v>0.48553383310158793</v>
+        <v>0.43619763297949987</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>698.0498</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.454144701031019</v>
+        <v>21.731049843955017</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.0458552989689807</v>
+        <v>-1.7689501560449834</v>
       </c>
       <c r="G66" s="0">
-        <v>2.0458552989689807</v>
+        <v>1.7689501560449834</v>
       </c>
       <c r="H66" s="0">
-        <v>20.954144701031019</v>
+        <v>21.231049843955017</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.5458552989689807</v>
+        <v>-2.2689501560449834</v>
       </c>
       <c r="J66" s="0">
-        <v>2.5458552989689807</v>
+        <v>2.2689501560449834</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>634.08339999999998</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.319062615765738</v>
+        <v>20.297274715607877</v>
       </c>
       <c r="F67" s="0">
-        <v>-1.1809373842342623</v>
+        <v>-1.2027252843921232</v>
       </c>
       <c r="G67" s="0">
-        <v>1.1809373842342623</v>
+        <v>1.2027252843921232</v>
       </c>
       <c r="H67" s="0">
-        <v>19.819062615765738</v>
+        <v>19.797274715607877</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.6809373842342623</v>
+        <v>-1.7027252843921232</v>
       </c>
       <c r="J67" s="0">
-        <v>1.6809373842342623</v>
+        <v>1.7027252843921232</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>578.7296</v>
+        <v>581.15859999999998</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>19.924030575958984</v>
+        <v>19.88683142605117</v>
       </c>
       <c r="F68" s="0">
-        <v>0.92403057595898375</v>
+        <v>0.88683142605117027</v>
       </c>
       <c r="G68" s="0">
-        <v>0.92403057595898375</v>
+        <v>0.88683142605117027</v>
       </c>
       <c r="H68" s="0">
-        <v>19.424030575958984</v>
+        <v>19.38683142605117</v>
       </c>
       <c r="I68" s="0">
-        <v>0.42403057595898375</v>
+        <v>0.38683142605117027</v>
       </c>
       <c r="J68" s="0">
-        <v>0.42403057595898375</v>
+        <v>0.38683142605117027</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3476,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.1910000000000001</v>
+        <v>1.155</v>
       </c>
       <c r="C2" s="0">
-        <v>1.4890000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="D2" s="0">
-        <v>0.312</v>
+        <v>0.34599999999999998</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.062</v>
+        <v>-0.049000000000000002</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3501,16 +3501,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="0">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0">
         <v>0.001</v>
       </c>
-      <c r="E3" s="0">
-        <v>0.002</v>
-      </c>
       <c r="F3" s="0">
         <v>0</v>
       </c>
       <c r="G3" s="0">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.236</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.56200000000000006</v>
+        <v>-0.54900000000000004</v>
       </c>
       <c r="F5" s="0">
-        <v>49.299999999999997</v>
+        <v>55.200000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>37.5</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3548,16 +3548,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.184</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>1.4410000000000001</v>
+        <v>1.407</v>
       </c>
       <c r="D6" s="0">
-        <v>0.35299999999999998</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.0040000000000000001</v>
+        <v>-0.0070000000000000001</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3567,18 +3567,18 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.196</v>
+        <v>1.1719999999999999</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.504</v>
+        <v>-0.50700000000000001</v>
       </c>
       <c r="F7" s="0">
-        <v>47.799999999999997</v>
+        <v>49.299999999999997</v>
       </c>
       <c r="G7" s="0">
-        <v>40.299999999999997</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>8.9078999999999997</v>
+        <v>8.6630000000000003</v>
       </c>
       <c r="C2" s="0">
-        <v>1.6880999999999999</v>
+        <v>1.6577</v>
       </c>
       <c r="D2" s="0">
-        <v>5.2770000000000001</v>
+        <v>5.226</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0184</v>
+        <v>0.018800000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025999999999999999</v>
+        <v>0.0025000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>7.1180000000000003</v>
+        <v>7.3979999999999997</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>0.3347</v>
+        <v>0.32869999999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>0.3372</v>
+        <v>0.33139999999999997</v>
       </c>
       <c r="D4" s="0">
-        <v>0.99299999999999999</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="E4" s="0">
-        <v>0.32469999999999999</v>
+        <v>0.32500000000000001</v>
       </c>
     </row>
   </sheetData>
